--- a/assessment_forms/050_property_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/050_property_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>property_assessment_form_page_1</t>
+          <t>property_location</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>property_assessment_form_page_1_label</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>property_location</t>
+          <t>property_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>property_location</t>
+          <t>Property Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>property_type</t>
+          <t>property_age</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>property_type</t>
+          <t>Property Age</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>property_age</t>
+          <t>property_assessment_value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>property_age</t>
+          <t>Property Assessment Value</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>property_assessment_date</t>
+          <t>property_condition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>property_assessment_date</t>
+          <t>Property Condition</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>property_assessment_value</t>
+          <t>property_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>property_assessment_value</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>property_condition</t>
+          <t>property_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>property_condition</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>property_features</t>
+          <t>property_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>property_features</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>property_comments</t>
+          <t>property_assessment_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>property_comments</t>
+          <t>Assessment Date Range</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>property_email</t>
+          <t>property_assessment_price</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>property_email</t>
+          <t>Assessment Price Range</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>property_phone</t>
+          <t>property_assessment_value_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>property_phone</t>
+          <t>Assessment Value Range</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>property_address</t>
+          <t>property_assessment_notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>property_address</t>
+          <t>Assessment Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>property_assessment_status</t>
+          <t>Assessment Status</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>property_assessment_notes</t>
+          <t>property_assessment_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>property_assessment_notes</t>
+          <t>Assessment Time</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>property_assessment_recommendations</t>
+          <t>property_assessment_date_range</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>property_assessment_recommendations</t>
+          <t>Property Assessment Date Range</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>property_assessment_comments</t>
+          <t>property_assessment_time_range</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>property_assessment_comments</t>
+          <t>Assessment Time Range</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>property_assessment_date_range</t>
+          <t>property_assessment_price_range</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>property_assessment_date_range</t>
+          <t>Property Assessment Price Range</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>property_assessment_time_range</t>
+          <t>property_assessment_value_range</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>property_assessment_time_range</t>
+          <t>Property Assessment Value Range</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>property_assessment_price</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>property_assessment_price</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>property_assessment_value_range</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>property_assessment_value_range</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>property_assessment_status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>property_assessment_status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>property_assessment_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>property_assessment_date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>property_assessment_time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>property_assessment_time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>property_assessment_price_range</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>property_assessment_price_range</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>property_assessment_value</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>property_assessment_value</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1267,63 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>property_assessment_status_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>property_assessment_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>property_assessment_status_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
